--- a/Graphs and Images/DataGraphs.xlsx
+++ b/Graphs and Images/DataGraphs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AdvRendering-GitWikiTemplate\Graphs and Images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390991C9-C7F1-46A4-BA29-AF3573147A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA61E08-E3E0-43DA-8458-2B2EA3763ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{DC657A5A-711A-4118-BBB5-34FD2B6C568B}"/>
   </bookViews>
@@ -3124,7 +3124,7 @@
                 </c:marker>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>frameTimes_base_7x7_400x300!$C$2:$C$101</c15:sqref>
@@ -3438,7 +3438,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001B-67AA-4B08-8A5F-D15C45EC8513}"/>
                   </c:ext>
@@ -20422,15 +20422,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>4760</xdr:colOff>
+      <xdr:colOff>4761</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>4760</xdr:rowOff>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>588390</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20460,13 +20460,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>180976</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>100014</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>52390</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>48898</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20496,15 +20496,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>90489</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>61915</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>593913</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>57649</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20534,15 +20534,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>110</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>90489</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>61915</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>62809</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -21107,7 +21107,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{2C228387-B384-40DB-BBF2-0E1DAFACD9BD}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{34D2290E-3605-496C-BC3B-B3C36D9923CF}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{2A042A38-5E66-4904-A77E-9A652736EEC3}" uniqueName="3" name="Column1" queryTableFieldId="3" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{2A042A38-5E66-4904-A77E-9A652736EEC3}" uniqueName="3" name="Column1" queryTableFieldId="3" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21119,7 +21119,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{06C85873-C64B-4149-905D-2317790BDE2D}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{FAFB9308-5091-46E1-9DB4-29FD744BA3E6}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{3964AF31-33BF-4CF6-B573-72B612AACEC7}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{3964AF31-33BF-4CF6-B573-72B612AACEC7}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21131,7 +21131,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E6D0BF36-7E80-4821-9EB8-26791C1CF0F9}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{5D9FC50B-2DD3-4B7F-AB46-5CCB4E781A06}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{64A0E63A-FA54-471D-B2A9-4E819935C603}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{64A0E63A-FA54-471D-B2A9-4E819935C603}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21143,7 +21143,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{40FAA385-BAF6-4A89-9CCA-14B34A4E0322}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{C87B7EBC-A1CC-47AA-9B5A-C4BC829A7E29}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{EB7AA39A-0C17-4AC1-B0E2-E969336F2634}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{EB7AA39A-0C17-4AC1-B0E2-E969336F2634}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21155,7 +21155,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{30A54A7E-2410-4821-B634-B62173B71B58}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{FC6ACBD2-065B-424C-B715-2EFDFBE75391}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{D09E808E-16F9-4518-8C93-D966CE0AA43F}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{D09E808E-16F9-4518-8C93-D966CE0AA43F}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21167,7 +21167,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7F1BA859-435A-4FF5-928B-B2E298F601BC}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{A1B574FC-E7FD-43E7-A3ED-234D95F891DA}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{087A5FAC-0C82-44ED-A06C-147B8623088A}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{087A5FAC-0C82-44ED-A06C-147B8623088A}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21179,7 +21179,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{4D2C048D-9E55-449B-8846-913EAE7730C6}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{EE1D32A8-D0DE-419F-A65D-E72ED1858E2C}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{7089EF6E-9784-4C32-906F-EDCFF08A8146}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{7089EF6E-9784-4C32-906F-EDCFF08A8146}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21191,7 +21191,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{81788461-B750-4B8E-AF82-664D73088FF3}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{C4B7F317-B327-4066-B1AD-8BB6CB662E8D}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{D843403C-01EC-4A40-BD19-3D5E010EE0D2}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{D843403C-01EC-4A40-BD19-3D5E010EE0D2}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21203,7 +21203,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DBE8F64D-9C01-49A5-A081-5AFE1A91E2DD}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{E6ED1D72-4458-44F0-8B6D-418172E53E05}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{6D16DD1C-D6C9-4A0D-9A70-0AF5D4DB6579}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{6D16DD1C-D6C9-4A0D-9A70-0AF5D4DB6579}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21215,7 +21215,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{96295DE3-BED5-4F15-8D2D-71B6F1258EFD}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{98523DF9-3B07-4123-9324-95CB65EC050E}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{56B8CBB8-3C9F-49B1-A90E-6D3C9913FCE1}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{56B8CBB8-3C9F-49B1-A90E-6D3C9913FCE1}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21227,7 +21227,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A2129787-5864-431C-905F-522017F14FE9}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{98C534EB-77EC-4663-853C-5F711587F262}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{9D9FF339-899D-4A74-9327-55B5C1D07BC7}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{9D9FF339-899D-4A74-9327-55B5C1D07BC7}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21239,7 +21239,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{9C7D9314-E26D-4CEC-B1FC-7409322BCE03}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{D5AB14C6-5D99-4D77-86E5-6302FDAA1536}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{1897672B-EC12-402F-B69A-60B281D4B4D6}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{1897672B-EC12-402F-B69A-60B281D4B4D6}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21251,7 +21251,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C770FA5E-1185-4D46-A80F-E60066D2FD9C}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{396D7BF8-2750-49FD-BA0B-314EF7BE97F3}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{D1795C26-FF12-495F-9647-301B1E0EE9EC}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{D1795C26-FF12-495F-9647-301B1E0EE9EC}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21263,7 +21263,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{084E5DB2-2A9B-4FC1-8046-D7E3D1EA3EF0}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{DDF976FB-788A-477E-9C2A-6194F4AB7076}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{68DE45E8-7F11-4B8A-B5F5-45CB1EF3F5BB}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{68DE45E8-7F11-4B8A-B5F5-45CB1EF3F5BB}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21275,7 +21275,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{13DF4DC9-1A4A-4492-BAB1-C03BF6A21AA9}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{3E7DF94F-3D8F-4285-B0BF-6507C26B6419}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{5C214A91-E64A-44AC-8B14-976D797F8ADE}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{5C214A91-E64A-44AC-8B14-976D797F8ADE}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21287,7 +21287,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5B6B12BB-79A0-43A7-9599-EF35A126EEE9}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{7654CA85-7B53-4EF0-873B-93F599CA5252}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{D7667831-403B-4806-8FDA-E1A930E3EC92}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{D7667831-403B-4806-8FDA-E1A930E3EC92}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21299,7 +21299,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{88A90F9E-F03E-40CD-BCE6-16D16CD38FA9}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{406653D2-8854-4B8E-912F-A3C9C4E815AE}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{AD6EEA4B-E21D-4232-BCD6-9636D9C6766F}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{AD6EEA4B-E21D-4232-BCD6-9636D9C6766F}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21311,7 +21311,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{131A899F-3BC1-44AF-A1D4-FF03714F883E}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{B9CD0343-6B4A-4F9B-A38B-7006052C16FD}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{BFBFEF46-443C-40A6-9DC6-4146FBDEC01E}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{BFBFEF46-443C-40A6-9DC6-4146FBDEC01E}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21323,7 +21323,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3F9F7A26-65D5-4242-A90B-F4364F799AA5}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{ACA2585B-F0A5-49FF-A34E-04557B70A892}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{9CE4952F-ECBB-4480-9E97-CA40D907CD1E}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{9CE4952F-ECBB-4480-9E97-CA40D907CD1E}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21335,7 +21335,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3F521E7E-113B-4DE4-B061-8F1585547847}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{EB2518BE-E3E5-48C4-B456-A6FF6D8F6A83}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{4433568B-8CD6-4932-9A8B-D190773A8E0C}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{4433568B-8CD6-4932-9A8B-D190773A8E0C}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21347,7 +21347,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{20DA019A-231D-4D2A-ADA7-08C1ED8ECA56}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{FAC01D9C-C2E8-4704-B5DD-9099202FD776}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{D7CD7945-AF15-4A52-A448-27C3BFC70C20}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{D7CD7945-AF15-4A52-A448-27C3BFC70C20}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21359,7 +21359,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5F976753-9E0D-46CD-B1A4-1F56DD15AD1F}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{B1C6B2DC-B2D3-441D-ADCA-F89358613928}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{92A12FAA-47FD-43E5-A8DA-6C0737F5A70B}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{92A12FAA-47FD-43E5-A8DA-6C0737F5A70B}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21371,7 +21371,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DD434D4E-633E-4211-8DAF-31A07A7A0FA0}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{59B3D2B6-130B-4703-BF19-2C06FBCA6D9B}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{806BBA78-EBB6-4C5E-B228-9AACDF20D32D}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{806BBA78-EBB6-4C5E-B228-9AACDF20D32D}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21383,7 +21383,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FD1BF1C3-81AE-4C88-94FE-5F093AD6999B}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{AC85A708-18F5-4DC4-BC9F-7001870513CF}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{ED7E5BF2-CA10-4075-946C-9698D829A4E2}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{ED7E5BF2-CA10-4075-946C-9698D829A4E2}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21395,7 +21395,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A2FF0255-3435-481A-AF58-0E78336A3E63}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{2E70447A-47C6-4ED1-85E6-FFB423D72C40}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{CEFB398C-6816-4035-9DFD-49638B3C4C91}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{CEFB398C-6816-4035-9DFD-49638B3C4C91}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21407,7 +21407,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{50C553D6-26AF-4765-9C61-4DC1598BEE48}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{92069465-81EF-44D6-B5A2-A8CD3871080E}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{A8AB94FC-9B88-4AA2-9552-0F5085AA8309}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{A8AB94FC-9B88-4AA2-9552-0F5085AA8309}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21419,7 +21419,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{23F6A484-3D2E-4E45-A7EF-9FCD7A2ADF40}" uniqueName="1" name="Frame" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{8802A1CB-DFF2-4EF7-9DE5-325862BBBA8E}" uniqueName="2" name="DeltaTime" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{83E83B4C-0606-4749-A350-DEBA4F1BEDAC}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{83E83B4C-0606-4749-A350-DEBA4F1BEDAC}" uniqueName="3" name="FPS" queryTableFieldId="3" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
